--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/78.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/78.xlsx
@@ -426,13 +426,13 @@
         <v>2.319585147944322</v>
       </c>
       <c r="E2">
-        <v>-7.723264683575312</v>
+        <v>-3.557448988335228</v>
       </c>
       <c r="F2">
-        <v>-3.005266554192543</v>
+        <v>-2.481497300709041</v>
       </c>
       <c r="G2">
-        <v>-10.03074570018436</v>
+        <v>-8.289726259521437</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>2.809944956531376</v>
       </c>
       <c r="E3">
-        <v>-7.393963110685539</v>
+        <v>-4.323766416861221</v>
       </c>
       <c r="F3">
-        <v>-2.816674632699388</v>
+        <v>-2.226930057419919</v>
       </c>
       <c r="G3">
-        <v>-10.30266381203711</v>
+        <v>-8.178932532345227</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.193086875699384</v>
       </c>
       <c r="E4">
-        <v>-8.261138712310366</v>
+        <v>-5.31307043399891</v>
       </c>
       <c r="F4">
-        <v>-2.865317194959178</v>
+        <v>-2.146283520552971</v>
       </c>
       <c r="G4">
-        <v>-10.42520759361769</v>
+        <v>-8.137579297031545</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.394146109855618</v>
       </c>
       <c r="E5">
-        <v>-8.90851124255089</v>
+        <v>-5.465684536531409</v>
       </c>
       <c r="F5">
-        <v>-2.857008669909099</v>
+        <v>-2.204791938580103</v>
       </c>
       <c r="G5">
-        <v>-9.958293046930264</v>
+        <v>-8.394941910046592</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.445887615016879</v>
       </c>
       <c r="E6">
-        <v>-9.364768584245702</v>
+        <v>-6.399048314252346</v>
       </c>
       <c r="F6">
-        <v>-2.673026613012523</v>
+        <v>-2.503934460181269</v>
       </c>
       <c r="G6">
-        <v>-10.24748350907192</v>
+        <v>-7.698039981814569</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.364373136032831</v>
       </c>
       <c r="E7">
-        <v>-9.932933575618064</v>
+        <v>-7.002961079441257</v>
       </c>
       <c r="F7">
-        <v>-2.744780625810419</v>
+        <v>-2.26214809754994</v>
       </c>
       <c r="G7">
-        <v>-10.62378384117372</v>
+        <v>-7.870694579050991</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.190608856225164</v>
       </c>
       <c r="E8">
-        <v>-10.59101594688673</v>
+        <v>-7.417022100332597</v>
       </c>
       <c r="F8">
-        <v>-2.628853092890837</v>
+        <v>-1.941518553887558</v>
       </c>
       <c r="G8">
-        <v>-10.56013470536361</v>
+        <v>-7.89882449148011</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>2.96566821363891</v>
       </c>
       <c r="E9">
-        <v>-11.92327941452132</v>
+        <v>-8.810456194862804</v>
       </c>
       <c r="F9">
-        <v>-2.427326214402968</v>
+        <v>-1.925991635289484</v>
       </c>
       <c r="G9">
-        <v>-10.33693289000395</v>
+        <v>-8.109173761991432</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>2.74175515293963</v>
       </c>
       <c r="E10">
-        <v>-11.77150307968024</v>
+        <v>-9.680729272708877</v>
       </c>
       <c r="F10">
-        <v>-2.571842363127967</v>
+        <v>-2.157941963379971</v>
       </c>
       <c r="G10">
-        <v>-10.26769911509966</v>
+        <v>-7.564307234716281</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>2.566076206458226</v>
       </c>
       <c r="E11">
-        <v>-11.64592849544754</v>
+        <v>-10.35497376771092</v>
       </c>
       <c r="F11">
-        <v>-2.229584974945892</v>
+        <v>-1.719756316484103</v>
       </c>
       <c r="G11">
-        <v>-9.035531513875425</v>
+        <v>-7.006962221850561</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.47781311657254</v>
       </c>
       <c r="E12">
-        <v>-13.53937404753468</v>
+        <v>-10.23214796720087</v>
       </c>
       <c r="F12">
-        <v>-2.204330537936743</v>
+        <v>-1.664036183134794</v>
       </c>
       <c r="G12">
-        <v>-8.795280471292882</v>
+        <v>-6.32836950992024</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.496971029945079</v>
       </c>
       <c r="E13">
-        <v>-13.28956530737555</v>
+        <v>-11.32576991157926</v>
       </c>
       <c r="F13">
-        <v>-1.986280214865232</v>
+        <v>-1.257187675086831</v>
       </c>
       <c r="G13">
-        <v>-8.184172643175661</v>
+        <v>-6.319014747254263</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.624393983443909</v>
       </c>
       <c r="E14">
-        <v>-14.38338650461027</v>
+        <v>-12.02040159656383</v>
       </c>
       <c r="F14">
-        <v>-1.832434164082503</v>
+        <v>-1.083798780537255</v>
       </c>
       <c r="G14">
-        <v>-8.140952392794654</v>
+        <v>-6.122193953232531</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.840734330985684</v>
       </c>
       <c r="E15">
-        <v>-14.90880270135022</v>
+        <v>-12.17383988136572</v>
       </c>
       <c r="F15">
-        <v>-1.521474981480402</v>
+        <v>-0.4736540012290427</v>
       </c>
       <c r="G15">
-        <v>-7.156907484674066</v>
+        <v>-6.048523966779879</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.107796299921304</v>
       </c>
       <c r="E16">
-        <v>-15.55433667114363</v>
+        <v>-13.11701686226128</v>
       </c>
       <c r="F16">
-        <v>-1.243554404371556</v>
+        <v>-0.7872647878875046</v>
       </c>
       <c r="G16">
-        <v>-6.91088477336846</v>
+        <v>-5.938419296131151</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.374457000240957</v>
       </c>
       <c r="E17">
-        <v>-16.37101978758293</v>
+        <v>-13.51719811031911</v>
       </c>
       <c r="F17">
-        <v>-1.142348616934527</v>
+        <v>-0.03756329549485413</v>
       </c>
       <c r="G17">
-        <v>-6.463838023223475</v>
+        <v>-4.097624470288631</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.589403560355813</v>
       </c>
       <c r="E18">
-        <v>-17.05769947221004</v>
+        <v>-15.38987608060707</v>
       </c>
       <c r="F18">
-        <v>-0.6070998479830291</v>
+        <v>0.0531926371558597</v>
       </c>
       <c r="G18">
-        <v>-6.831009996946897</v>
+        <v>-4.370005234381256</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.712541823820777</v>
       </c>
       <c r="E19">
-        <v>-17.54123181285305</v>
+        <v>-16.41318440906835</v>
       </c>
       <c r="F19">
-        <v>-0.2196715853262974</v>
+        <v>0.1835163671686947</v>
       </c>
       <c r="G19">
-        <v>-5.670658491994224</v>
+        <v>-3.658505151431263</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.722019570975768</v>
       </c>
       <c r="E20">
-        <v>-18.7670806697814</v>
+        <v>-16.97537181475059</v>
       </c>
       <c r="F20">
-        <v>0.122333979165326</v>
+        <v>0.4699467626064994</v>
       </c>
       <c r="G20">
-        <v>-5.566870172847429</v>
+        <v>-2.964234762889915</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.617112282537508</v>
       </c>
       <c r="E21">
-        <v>-19.34619551130431</v>
+        <v>-17.69192131393228</v>
       </c>
       <c r="F21">
-        <v>0.5361598258470694</v>
+        <v>0.6550032120245062</v>
       </c>
       <c r="G21">
-        <v>-5.425981081527992</v>
+        <v>-3.878826054261738</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.415343825130363</v>
       </c>
       <c r="E22">
-        <v>-18.99123560468707</v>
+        <v>-16.58197874923026</v>
       </c>
       <c r="F22">
-        <v>0.4185068036274557</v>
+        <v>0.7920276059585863</v>
       </c>
       <c r="G22">
-        <v>-5.145617105381239</v>
+        <v>-3.456001281668573</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.147196456444009</v>
       </c>
       <c r="E23">
-        <v>-20.94764505937685</v>
+        <v>-18.04027417697233</v>
       </c>
       <c r="F23">
-        <v>0.4373107436710045</v>
+        <v>1.312154527971979</v>
       </c>
       <c r="G23">
-        <v>-5.492819564693881</v>
+        <v>-3.439224395835133</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.85043967413996</v>
       </c>
       <c r="E24">
-        <v>-21.07009499654426</v>
+        <v>-19.85078978455699</v>
       </c>
       <c r="F24">
-        <v>0.8910904069245736</v>
+        <v>0.9093774457087755</v>
       </c>
       <c r="G24">
-        <v>-5.208587028328542</v>
+        <v>-2.962876337164305</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.562998287186047</v>
       </c>
       <c r="E25">
-        <v>-20.90594234224021</v>
+        <v>-18.41449821201819</v>
       </c>
       <c r="F25">
-        <v>0.7580181538692499</v>
+        <v>1.530595012090209</v>
       </c>
       <c r="G25">
-        <v>-5.822680768064858</v>
+        <v>-2.404579770046346</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.315134231809628</v>
       </c>
       <c r="E26">
-        <v>-20.7952936083368</v>
+        <v>-19.49019645627422</v>
       </c>
       <c r="F26">
-        <v>0.7362619124021237</v>
+        <v>1.846151633777847</v>
       </c>
       <c r="G26">
-        <v>-5.563123017826543</v>
+        <v>-3.401555972332707</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.125816381600874</v>
       </c>
       <c r="E27">
-        <v>-21.17464387595934</v>
+        <v>-20.1520102901252</v>
       </c>
       <c r="F27">
-        <v>0.7484786748586107</v>
+        <v>1.293498037326129</v>
       </c>
       <c r="G27">
-        <v>-5.488534289337246</v>
+        <v>-3.16104243202541</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.000509408731608</v>
       </c>
       <c r="E28">
-        <v>-21.00151125769809</v>
+        <v>-18.9606729336093</v>
       </c>
       <c r="F28">
-        <v>0.6568612401089854</v>
+        <v>1.417496353851187</v>
       </c>
       <c r="G28">
-        <v>-5.716090285706296</v>
+        <v>-4.198272660403038</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.933186163472011</v>
       </c>
       <c r="E29">
-        <v>-20.59955937630326</v>
+        <v>-19.07548786359978</v>
       </c>
       <c r="F29">
-        <v>0.9717883025704959</v>
+        <v>1.170384417187261</v>
       </c>
       <c r="G29">
-        <v>-5.788103255271429</v>
+        <v>-4.482797225487167</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.909172841007013</v>
       </c>
       <c r="E30">
-        <v>-20.24421907786938</v>
+        <v>-18.51499410719641</v>
       </c>
       <c r="F30">
-        <v>0.6979598604314801</v>
+        <v>1.216758081130783</v>
       </c>
       <c r="G30">
-        <v>-5.881516351847261</v>
+        <v>-3.574791345785151</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.911100928052762</v>
       </c>
       <c r="E31">
-        <v>-20.64804574750339</v>
+        <v>-18.69392770066149</v>
       </c>
       <c r="F31">
-        <v>0.8440755866112849</v>
+        <v>1.084916782036019</v>
       </c>
       <c r="G31">
-        <v>-5.996418168415897</v>
+        <v>-3.837876409199868</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.917847262834772</v>
       </c>
       <c r="E32">
-        <v>-19.94015921909837</v>
+        <v>-18.12772353853445</v>
       </c>
       <c r="F32">
-        <v>0.5171827570163355</v>
+        <v>1.149496304758268</v>
       </c>
       <c r="G32">
-        <v>-6.281382417188992</v>
+        <v>-3.25960376522801</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.906510722827821</v>
       </c>
       <c r="E33">
-        <v>-19.47993040569883</v>
+        <v>-18.5070194644689</v>
       </c>
       <c r="F33">
-        <v>0.7651172625112416</v>
+        <v>1.270615216191195</v>
       </c>
       <c r="G33">
-        <v>-6.159652378555152</v>
+        <v>-3.673457678077653</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.854181596616598</v>
       </c>
       <c r="E34">
-        <v>-19.60753374628696</v>
+        <v>-17.71605808039317</v>
       </c>
       <c r="F34">
-        <v>0.3875399450086018</v>
+        <v>1.524294449624516</v>
       </c>
       <c r="G34">
-        <v>-5.970253707700884</v>
+        <v>-4.103117235179141</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.742818604569071</v>
       </c>
       <c r="E35">
-        <v>-19.63995309170787</v>
+        <v>-16.84967043324567</v>
       </c>
       <c r="F35">
-        <v>0.5928441788532368</v>
+        <v>0.8744683866199987</v>
       </c>
       <c r="G35">
-        <v>-5.921990219783011</v>
+        <v>-3.781075182784321</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.556143481107279</v>
       </c>
       <c r="E36">
-        <v>-19.21135566925191</v>
+        <v>-17.22212836342855</v>
       </c>
       <c r="F36">
-        <v>0.6611811761145848</v>
+        <v>1.377045516837681</v>
       </c>
       <c r="G36">
-        <v>-5.542303667031867</v>
+        <v>-2.854294153319161</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.283283721960181</v>
       </c>
       <c r="E37">
-        <v>-18.77837921243053</v>
+        <v>-17.98663440235147</v>
       </c>
       <c r="F37">
-        <v>0.6488003969123435</v>
+        <v>1.340040688219822</v>
       </c>
       <c r="G37">
-        <v>-5.675468762800371</v>
+        <v>-3.664706660178614</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9190739278615949</v>
       </c>
       <c r="E38">
-        <v>-18.92417343310748</v>
+        <v>-18.39383025664718</v>
       </c>
       <c r="F38">
-        <v>0.8827984492225506</v>
+        <v>0.9484465658944113</v>
       </c>
       <c r="G38">
-        <v>-6.019921558446199</v>
+        <v>-2.71738518375133</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.4658386351412144</v>
       </c>
       <c r="E39">
-        <v>-18.13363319711446</v>
+        <v>-16.4185280083974</v>
       </c>
       <c r="F39">
-        <v>0.7937555803608262</v>
+        <v>1.21363844949184</v>
       </c>
       <c r="G39">
-        <v>-5.555166055544889</v>
+        <v>-3.177048230792381</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.0694456045023108</v>
       </c>
       <c r="E40">
-        <v>-17.79790119113379</v>
+        <v>-16.09511798019161</v>
       </c>
       <c r="F40">
-        <v>0.7962274286907799</v>
+        <v>1.332605262412293</v>
       </c>
       <c r="G40">
-        <v>-5.321415112871608</v>
+        <v>-2.858540054017082</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.6724489089609506</v>
       </c>
       <c r="E41">
-        <v>-18.12192256333062</v>
+        <v>-14.88561238595694</v>
       </c>
       <c r="F41">
-        <v>0.6376041830961053</v>
+        <v>1.447375566070165</v>
       </c>
       <c r="G41">
-        <v>-5.213006833769113</v>
+        <v>-2.544674805748398</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.322295120508663</v>
       </c>
       <c r="E42">
-        <v>-17.03457255545286</v>
+        <v>-15.66833194733872</v>
       </c>
       <c r="F42">
-        <v>0.8425232260984387</v>
+        <v>1.278499617131041</v>
       </c>
       <c r="G42">
-        <v>-4.913874270302336</v>
+        <v>-2.801286019026331</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.992662419327608</v>
       </c>
       <c r="E43">
-        <v>-16.93734169003417</v>
+        <v>-14.4906207691119</v>
       </c>
       <c r="F43">
-        <v>0.7455429407830892</v>
+        <v>0.9866707513291918</v>
       </c>
       <c r="G43">
-        <v>-5.380585381253074</v>
+        <v>-3.166275980412724</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.656423985815902</v>
       </c>
       <c r="E44">
-        <v>-16.90117276813491</v>
+        <v>-15.39275166160194</v>
       </c>
       <c r="F44">
-        <v>0.6663029717660942</v>
+        <v>1.06136961024404</v>
       </c>
       <c r="G44">
-        <v>-5.091608198512778</v>
+        <v>-1.643369180470767</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.286894092041723</v>
       </c>
       <c r="E45">
-        <v>-15.88787236723058</v>
+        <v>-14.20737830535414</v>
       </c>
       <c r="F45">
-        <v>0.68266488470619</v>
+        <v>1.242652846142295</v>
       </c>
       <c r="G45">
-        <v>-5.113096918505581</v>
+        <v>-2.329403702897908</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.859697936535927</v>
       </c>
       <c r="E46">
-        <v>-16.21631353005889</v>
+        <v>-14.96619658092344</v>
       </c>
       <c r="F46">
-        <v>0.466436141553435</v>
+        <v>1.238587218929355</v>
       </c>
       <c r="G46">
-        <v>-4.875848193649931</v>
+        <v>-1.832748163995678</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.357120035276631</v>
       </c>
       <c r="E47">
-        <v>-15.40635066904697</v>
+        <v>-14.30378498850344</v>
       </c>
       <c r="F47">
-        <v>0.6068054830600197</v>
+        <v>1.023821372609944</v>
       </c>
       <c r="G47">
-        <v>-4.369572113135409</v>
+        <v>-2.604839284262376</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.767045697924999</v>
       </c>
       <c r="E48">
-        <v>-15.54194676625865</v>
+        <v>-13.72796687605811</v>
       </c>
       <c r="F48">
-        <v>0.5950981665562542</v>
+        <v>0.8017924009027869</v>
       </c>
       <c r="G48">
-        <v>-4.635564338851795</v>
+        <v>-1.890392664352003</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.084521374790757</v>
       </c>
       <c r="E49">
-        <v>-14.76964722356852</v>
+        <v>-13.80855107102461</v>
       </c>
       <c r="F49">
-        <v>0.4528012141033552</v>
+        <v>1.11608990413817</v>
       </c>
       <c r="G49">
-        <v>-4.133235567873284</v>
+        <v>-1.9812923452133</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.309607686200814</v>
       </c>
       <c r="E50">
-        <v>-14.49665722496413</v>
+        <v>-11.45493104722603</v>
       </c>
       <c r="F50">
-        <v>0.3904582833686644</v>
+        <v>1.046137590441363</v>
       </c>
       <c r="G50">
-        <v>-4.287164233669955</v>
+        <v>-2.107849060761083</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.446868933712629</v>
       </c>
       <c r="E51">
-        <v>-14.31959841973822</v>
+        <v>-11.64718741122168</v>
       </c>
       <c r="F51">
-        <v>0.1604554470421593</v>
+        <v>1.033930768393709</v>
       </c>
       <c r="G51">
-        <v>-4.39066052409796</v>
+        <v>-2.072953269476388</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.50242467415088</v>
       </c>
       <c r="E52">
-        <v>-13.80212516640772</v>
+        <v>-11.66104454168515</v>
       </c>
       <c r="F52">
-        <v>0.1964082490584634</v>
+        <v>0.7210895350524479</v>
       </c>
       <c r="G52">
-        <v>-3.772517756957289</v>
+        <v>-1.128571767566366</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.485566876577607</v>
       </c>
       <c r="E53">
-        <v>-13.2898913575041</v>
+        <v>-12.16594675117035</v>
       </c>
       <c r="F53">
-        <v>0.1998086972469554</v>
+        <v>0.9211883081378909</v>
       </c>
       <c r="G53">
-        <v>-4.826954711192646</v>
+        <v>-1.748545456337208</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.406550845517386</v>
       </c>
       <c r="E54">
-        <v>-13.18843542583625</v>
+        <v>-11.04966432285759</v>
       </c>
       <c r="F54">
-        <v>0.3392701480800718</v>
+        <v>0.4776133029194088</v>
       </c>
       <c r="G54">
-        <v>-4.398076084822305</v>
+        <v>-1.95771348708713</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.276882962601589</v>
       </c>
       <c r="E55">
-        <v>-12.5738716897813</v>
+        <v>-11.48259096646488</v>
       </c>
       <c r="F55">
-        <v>0.3883542301655536</v>
+        <v>0.515379401180441</v>
       </c>
       <c r="G55">
-        <v>-4.721834216092716</v>
+        <v>-2.453660282132521</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.108846022297265</v>
       </c>
       <c r="E56">
-        <v>-12.73700996590762</v>
+        <v>-10.10569938748469</v>
       </c>
       <c r="F56">
-        <v>0.2034062968773137</v>
+        <v>0.7444378986677548</v>
       </c>
       <c r="G56">
-        <v>-4.597472637768201</v>
+        <v>-1.577331315365383</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.912884567299141</v>
       </c>
       <c r="E57">
-        <v>-12.45859485544204</v>
+        <v>-10.34686327076318</v>
       </c>
       <c r="F57">
-        <v>0.4110614374110937</v>
+        <v>0.8993840213614023</v>
       </c>
       <c r="G57">
-        <v>-4.963719307011861</v>
+        <v>-1.974519903914606</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.694709431343475</v>
       </c>
       <c r="E58">
-        <v>-11.65481336145059</v>
+        <v>-10.08317928624455</v>
       </c>
       <c r="F58">
-        <v>0.2686178639278992</v>
+        <v>0.4766946434697041</v>
       </c>
       <c r="G58">
-        <v>-5.092809125603535</v>
+        <v>-2.866428110645987</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.456532545522875</v>
       </c>
       <c r="E59">
-        <v>-11.47840665648179</v>
+        <v>-9.852304095911492</v>
       </c>
       <c r="F59">
-        <v>0.344227098618424</v>
+        <v>0.9657412205300595</v>
       </c>
       <c r="G59">
-        <v>-5.12611024321034</v>
+        <v>-2.646730639911807</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.201755759417066</v>
       </c>
       <c r="E60">
-        <v>-11.95549045013788</v>
+        <v>-10.0980281525157</v>
       </c>
       <c r="F60">
-        <v>0.23834186372298</v>
+        <v>1.066676131826374</v>
       </c>
       <c r="G60">
-        <v>-5.41719068897024</v>
+        <v>-2.403090095458359</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.935702743371801</v>
       </c>
       <c r="E61">
-        <v>-11.71453940513776</v>
+        <v>-8.452566365562609</v>
       </c>
       <c r="F61">
-        <v>0.5506985021336036</v>
+        <v>0.9299690026075657</v>
       </c>
       <c r="G61">
-        <v>-5.584542832166599</v>
+        <v>-3.171942650045885</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.662465506827932</v>
       </c>
       <c r="E62">
-        <v>-12.06834455088303</v>
+        <v>-9.398949506055597</v>
       </c>
       <c r="F62">
-        <v>0.246315728342328</v>
+        <v>1.178109771585769</v>
       </c>
       <c r="G62">
-        <v>-5.362643661766031</v>
+        <v>-3.125716800716428</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.38595963717249</v>
       </c>
       <c r="E63">
-        <v>-11.41268491320847</v>
+        <v>-7.617058382673419</v>
       </c>
       <c r="F63">
-        <v>0.2694338058196566</v>
+        <v>0.9450171248468214</v>
       </c>
       <c r="G63">
-        <v>-5.923680048886125</v>
+        <v>-3.675652815300921</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.112351929337546</v>
       </c>
       <c r="E64">
-        <v>-11.06862957200171</v>
+        <v>-8.750630524747471</v>
       </c>
       <c r="F64">
-        <v>0.3128667654832403</v>
+        <v>0.7889278551373106</v>
       </c>
       <c r="G64">
-        <v>-6.3185586574575</v>
+        <v>-4.716777853669611</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.850837597204082</v>
       </c>
       <c r="E65">
-        <v>-10.89536562799424</v>
+        <v>-9.056963677470339</v>
       </c>
       <c r="F65">
-        <v>0.3541559103083789</v>
+        <v>0.9161120726935355</v>
       </c>
       <c r="G65">
-        <v>-6.465475352781637</v>
+        <v>-5.297478601595459</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.609916826849084</v>
       </c>
       <c r="E66">
-        <v>-10.76080202285631</v>
+        <v>-8.934749220951332</v>
       </c>
       <c r="F66">
-        <v>0.2188379532240656</v>
+        <v>0.6108404606790561</v>
       </c>
       <c r="G66">
-        <v>-6.580597011194755</v>
+        <v>-4.370825539771117</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.395115289699673</v>
       </c>
       <c r="E67">
-        <v>-10.33762065531353</v>
+        <v>-9.227189015418668</v>
       </c>
       <c r="F67">
-        <v>0.3456808834103371</v>
+        <v>0.8929840548073733</v>
       </c>
       <c r="G67">
-        <v>-6.417585924121542</v>
+        <v>-4.759440296385511</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.209035227594724</v>
       </c>
       <c r="E68">
-        <v>-10.15712926678981</v>
+        <v>-8.552070524933148</v>
       </c>
       <c r="F68">
-        <v>0.3902246837610749</v>
+        <v>0.7535830747946612</v>
       </c>
       <c r="G68">
-        <v>-6.844640191304831</v>
+        <v>-5.02452690495149</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.053943486083629</v>
       </c>
       <c r="E69">
-        <v>-10.9462385049964</v>
+        <v>-8.068850648996667</v>
       </c>
       <c r="F69">
-        <v>0.1909360539955699</v>
+        <v>0.9121591034473763</v>
       </c>
       <c r="G69">
-        <v>-6.72001939647712</v>
+        <v>-5.323564312993044</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.93118551308425</v>
       </c>
       <c r="E70">
-        <v>-10.84912537990192</v>
+        <v>-8.278953729056541</v>
       </c>
       <c r="F70">
-        <v>0.4019079776101592</v>
+        <v>0.2952266816406249</v>
       </c>
       <c r="G70">
-        <v>-6.856278684176181</v>
+        <v>-5.34994205310942</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.840953261369483</v>
       </c>
       <c r="E71">
-        <v>-10.87677624219275</v>
+        <v>-8.234216934334766</v>
       </c>
       <c r="F71">
-        <v>0.04115728716058568</v>
+        <v>0.4478989358135878</v>
       </c>
       <c r="G71">
-        <v>-7.281364218423803</v>
+        <v>-5.295181746503848</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.782172850257047</v>
       </c>
       <c r="E72">
-        <v>-10.87746457024192</v>
+        <v>-9.525946031126706</v>
       </c>
       <c r="F72">
-        <v>0.2331057533698843</v>
+        <v>0.1203202180091204</v>
       </c>
       <c r="G72">
-        <v>-7.13383721588961</v>
+        <v>-5.550365628403422</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.755467578314353</v>
       </c>
       <c r="E73">
-        <v>-11.09215952294557</v>
+        <v>-7.998025315516704</v>
       </c>
       <c r="F73">
-        <v>0.08744314415941086</v>
+        <v>0.7699714954916467</v>
       </c>
       <c r="G73">
-        <v>-6.944888072388986</v>
+        <v>-5.933605744103446</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.761674048712696</v>
       </c>
       <c r="E74">
-        <v>-10.95057225462175</v>
+        <v>-8.434425298687881</v>
       </c>
       <c r="F74">
-        <v>-0.01394985431065143</v>
+        <v>0.561285865908784</v>
       </c>
       <c r="G74">
-        <v>-6.707025759101719</v>
+        <v>-4.876976933866381</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.799247545136916</v>
       </c>
       <c r="E75">
-        <v>-11.36537141677634</v>
+        <v>-8.495840463179906</v>
       </c>
       <c r="F75">
-        <v>0.05246947241321574</v>
+        <v>0.3782365507077605</v>
       </c>
       <c r="G75">
-        <v>-6.557418462098838</v>
+        <v>-4.249108626023515</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.863882290326064</v>
       </c>
       <c r="E76">
-        <v>-11.74896033607006</v>
+        <v>-9.117916937613582</v>
       </c>
       <c r="F76">
-        <v>0.01747177801233942</v>
+        <v>-0.08536423647339961</v>
       </c>
       <c r="G76">
-        <v>-6.373473181476367</v>
+        <v>-4.633067329245057</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.950510592356995</v>
       </c>
       <c r="E77">
-        <v>-11.58519260205667</v>
+        <v>-8.865454511685961</v>
       </c>
       <c r="F77">
-        <v>-0.08876716976409997</v>
+        <v>0.4909624436155228</v>
       </c>
       <c r="G77">
-        <v>-6.374506766267592</v>
+        <v>-4.389039600647594</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.052645191639269</v>
       </c>
       <c r="E78">
-        <v>-12.029947619772</v>
+        <v>-9.446942273588888</v>
       </c>
       <c r="F78">
-        <v>-0.2114682629363739</v>
+        <v>-0.08025238123072385</v>
       </c>
       <c r="G78">
-        <v>-6.318903185721242</v>
+        <v>-5.284258559932455</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.161423584924375</v>
       </c>
       <c r="E79">
-        <v>-12.62468569662137</v>
+        <v>-10.76153563564555</v>
       </c>
       <c r="F79">
-        <v>-0.2858448869315331</v>
+        <v>-0.2295299857870144</v>
       </c>
       <c r="G79">
-        <v>-6.130675910963696</v>
+        <v>-4.648843442502868</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.266680412953007</v>
       </c>
       <c r="E80">
-        <v>-13.97891226319317</v>
+        <v>-10.54390623178493</v>
       </c>
       <c r="F80">
-        <v>-0.34270071199008</v>
+        <v>-0.1798875840720456</v>
       </c>
       <c r="G80">
-        <v>-5.979726594343001</v>
+        <v>-4.433211405280839</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.358256301235754</v>
       </c>
       <c r="E81">
-        <v>-13.39105293836145</v>
+        <v>-11.28342867960754</v>
       </c>
       <c r="F81">
-        <v>-0.4605624827951993</v>
+        <v>-0.6029994293391715</v>
       </c>
       <c r="G81">
-        <v>-5.727715653691409</v>
+        <v>-5.28996460422433</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.427412632469504</v>
       </c>
       <c r="E82">
-        <v>-14.18777454137494</v>
+        <v>-11.11484264924999</v>
       </c>
       <c r="F82">
-        <v>-0.4816899934036007</v>
+        <v>-0.3288429537086471</v>
       </c>
       <c r="G82">
-        <v>-5.748275787982889</v>
+        <v>-3.791217438624564</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.466992248397425</v>
       </c>
       <c r="E83">
-        <v>-14.5586339202331</v>
+        <v>-13.08764517984753</v>
       </c>
       <c r="F83">
-        <v>-0.843040421852801</v>
+        <v>-0.3915619632442088</v>
       </c>
       <c r="G83">
-        <v>-6.057475139194043</v>
+        <v>-4.248573786909326</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.472117745748286</v>
       </c>
       <c r="E84">
-        <v>-16.03946303463734</v>
+        <v>-13.36370548382913</v>
       </c>
       <c r="F84">
-        <v>-0.7099201234881148</v>
+        <v>-0.2099498654870424</v>
       </c>
       <c r="G84">
-        <v>-6.049928329607321</v>
+        <v>-3.917669155082445</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.442127119150303</v>
       </c>
       <c r="E85">
-        <v>-16.57271801988457</v>
+        <v>-13.92436679377078</v>
       </c>
       <c r="F85">
-        <v>-0.8680654010913741</v>
+        <v>-0.4388749958225054</v>
       </c>
       <c r="G85">
-        <v>-5.755944002767312</v>
+        <v>-4.123090030811482</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.382411016665154</v>
       </c>
       <c r="E86">
-        <v>-17.25442544005125</v>
+        <v>-15.13505431972145</v>
       </c>
       <c r="F86">
-        <v>-0.7104121737253778</v>
+        <v>-0.8076293721179277</v>
       </c>
       <c r="G86">
-        <v>-5.597483969997048</v>
+        <v>-3.339370261338111</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.304610424725333</v>
       </c>
       <c r="E87">
-        <v>-19.06929743963129</v>
+        <v>-16.70851336995258</v>
       </c>
       <c r="F87">
-        <v>-0.9159591192190331</v>
+        <v>-0.5896817666043638</v>
       </c>
       <c r="G87">
-        <v>-5.165685056438802</v>
+        <v>-4.188159935556829</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.224238471893677</v>
       </c>
       <c r="E88">
-        <v>-20.02352842557957</v>
+        <v>-17.89229723182368</v>
       </c>
       <c r="F88">
-        <v>-0.9792182243012202</v>
+        <v>-0.8052643831829351</v>
       </c>
       <c r="G88">
-        <v>-5.501232616772297</v>
+        <v>-3.840770446615299</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.158293757030195</v>
       </c>
       <c r="E89">
-        <v>-21.34548961484672</v>
+        <v>-20.88896056471145</v>
       </c>
       <c r="F89">
-        <v>-1.374798450568902</v>
+        <v>-0.6756050038271454</v>
       </c>
       <c r="G89">
-        <v>-5.097694864505548</v>
+        <v>-3.449940865448279</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.124090064338733</v>
       </c>
       <c r="E90">
-        <v>-22.71509487914857</v>
+        <v>-20.73221649388396</v>
       </c>
       <c r="F90">
-        <v>-1.160611633064047</v>
+        <v>-0.3976206424282844</v>
       </c>
       <c r="G90">
-        <v>-5.746937049586636</v>
+        <v>-4.428443790354966</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.137095200252275</v>
       </c>
       <c r="E91">
-        <v>-24.43051706104616</v>
+        <v>-21.72981214692969</v>
       </c>
       <c r="F91">
-        <v>-1.219973269516063</v>
+        <v>-1.085029734497815</v>
       </c>
       <c r="G91">
-        <v>-5.205735646793384</v>
+        <v>-4.475644162487578</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.205859549931899</v>
       </c>
       <c r="E92">
-        <v>-26.6680451251841</v>
+        <v>-24.72579620871631</v>
       </c>
       <c r="F92">
-        <v>-1.461197999048293</v>
+        <v>-1.145737467979379</v>
       </c>
       <c r="G92">
-        <v>-5.622588596148359</v>
+        <v>-3.987454175208715</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.331067143549864</v>
       </c>
       <c r="E93">
-        <v>-28.41500812854511</v>
+        <v>-27.44828761128368</v>
       </c>
       <c r="F93">
-        <v>-1.713702607504444</v>
+        <v>-0.9838372009392302</v>
       </c>
       <c r="G93">
-        <v>-5.393759485814245</v>
+        <v>-4.019190150131664</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.506898692625544</v>
       </c>
       <c r="E94">
-        <v>-30.04969214735996</v>
+        <v>-29.79545682385833</v>
       </c>
       <c r="F94">
-        <v>-1.625902289746919</v>
+        <v>-1.325174272936795</v>
       </c>
       <c r="G94">
-        <v>-5.633065536587667</v>
+        <v>-3.894267482920485</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.723769456409701</v>
       </c>
       <c r="E95">
-        <v>-32.02445550720282</v>
+        <v>-32.85784869273043</v>
       </c>
       <c r="F95">
-        <v>-1.707292700541581</v>
+        <v>-1.564603930307158</v>
       </c>
       <c r="G95">
-        <v>-5.583460029051982</v>
+        <v>-4.570455059447733</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.966920268207412</v>
       </c>
       <c r="E96">
-        <v>-34.47972845128858</v>
+        <v>-34.04736560269524</v>
       </c>
       <c r="F96">
-        <v>-1.919842664058504</v>
+        <v>-1.697222238025748</v>
       </c>
       <c r="G96">
-        <v>-5.503020882522194</v>
+        <v>-4.998385412787394</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.219085156832772</v>
       </c>
       <c r="E97">
-        <v>-36.78659424519496</v>
+        <v>-35.86623850906106</v>
       </c>
       <c r="F97">
-        <v>-1.925909626916607</v>
+        <v>-2.047074098556688</v>
       </c>
       <c r="G97">
-        <v>-6.079971194205596</v>
+        <v>-4.791927671045573</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.461692946818713</v>
       </c>
       <c r="E98">
-        <v>-39.83985218199359</v>
+        <v>-39.40534736519462</v>
       </c>
       <c r="F98">
-        <v>-2.093702899660272</v>
+        <v>-1.713464037692437</v>
       </c>
       <c r="G98">
-        <v>-5.988175739858571</v>
+        <v>-4.522624692775707</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.680028440585008</v>
       </c>
       <c r="E99">
-        <v>-41.64442869591719</v>
+        <v>-42.15443449560904</v>
       </c>
       <c r="F99">
-        <v>-2.466105405997624</v>
+        <v>-2.355095890348462</v>
       </c>
       <c r="G99">
-        <v>-6.50469907530324</v>
+        <v>-5.621686260219512</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.862639546127535</v>
       </c>
       <c r="E100">
-        <v>-44.82156303919564</v>
+        <v>-43.3354763664685</v>
       </c>
       <c r="F100">
-        <v>-2.487634674796383</v>
+        <v>-2.097627704414736</v>
       </c>
       <c r="G100">
-        <v>-6.672799337015151</v>
+        <v>-5.325454296611284</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.004945612260364</v>
       </c>
       <c r="E101">
-        <v>-46.88923257177987</v>
+        <v>-46.43296843737405</v>
       </c>
       <c r="F101">
-        <v>-2.379920404675557</v>
+        <v>-2.590773871751546</v>
       </c>
       <c r="G101">
-        <v>-6.807080048113868</v>
+        <v>-6.084456624077357</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.102964503858643</v>
       </c>
       <c r="E102">
-        <v>-49.84805937221505</v>
+        <v>-49.51381610206441</v>
       </c>
       <c r="F102">
-        <v>-2.658265105894636</v>
+        <v>-3.07075065411865</v>
       </c>
       <c r="G102">
-        <v>-7.346276624534299</v>
+        <v>-5.235086173642618</v>
       </c>
     </row>
   </sheetData>
